--- a/school_surveys/013_hybrid_learning_survey--school_surveys.xlsx
+++ b/school_surveys/013_hybrid_learning_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you feel about using technology in school?</t>
+          <t>Question5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Have you ever been satisfied with hybrid learning?</t>
+          <t>Question12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How do you feel about hybrid learning?</t>
+          <t>Question18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1374,12 +1374,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1492,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question2_choices</t>
+          <t>question3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,29 +1543,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question3_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question5_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1645,29 +1645,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question7_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1696,29 +1696,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question8_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1747,29 +1747,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question9_choices</t>
+          <t>question11_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,29 +1798,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question11_choices</t>
+          <t>question12_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1849,29 +1849,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question12_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1900,29 +1900,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question13_choices</t>
+          <t>question14_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1951,29 +1951,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question14_choices</t>
+          <t>question15_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2002,29 +2002,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2053,29 +2053,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>question16_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2104,29 +2104,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>question17_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2155,29 +2155,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>question20_choices</t>
+          <t>question21_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2206,29 +2206,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>question21_choices</t>
+          <t>question22_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2257,29 +2257,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>question22_choices</t>
+          <t>question23_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2308,29 +2308,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>question23_choices</t>
+          <t>question24_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2359,29 +2359,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>question24_choices</t>
+          <t>question25_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,29 +2410,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>question25_choices</t>
+          <t>question26_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2461,29 +2461,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>question26_choices</t>
+          <t>question27_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2495,12 +2495,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2512,29 +2512,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>question27_choices</t>
+          <t>question28_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2563,29 +2563,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>question28_choices</t>
+          <t>question29_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2614,29 +2614,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>question29_choices</t>
+          <t>question30_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2648,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2665,29 +2665,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>question30_choices</t>
+          <t>question31_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2716,29 +2716,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>question31_choices</t>
+          <t>question32_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2767,29 +2767,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>question32_choices</t>
+          <t>question33_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2818,29 +2818,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>question33_choices</t>
+          <t>question34_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2869,29 +2869,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>question34_choices</t>
+          <t>question35_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2920,29 +2920,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>question35_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
